--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487493_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487493_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4374</v>
+        <v>5.2516</v>
       </c>
       <c r="E2" t="n">
-        <v>3.728</v>
+        <v>3.8897</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7094</v>
+        <v>1.3619</v>
       </c>
       <c r="G2" t="n">
         <v>4.1697</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7846</v>
+        <v>0.5989</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0194</v>
+        <v>0.1423</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8041</v>
+        <v>0.4566</v>
       </c>
       <c r="V2" t="n">
         <v>4.0083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8342</v>
+        <v>4.6934</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1139</v>
+        <v>5.6256</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2797</v>
+        <v>-0.9322</v>
       </c>
       <c r="G3" t="n">
         <v>1.3924</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5582</v>
+        <v>0.301</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6422</v>
+        <v>-0.1306</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4316</v>
       </c>
       <c r="V3" t="n">
         <v>1.8249</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8944</v>
+        <v>0.4892</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7708</v>
+        <v>-0.0984</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6653</v>
+        <v>0.5875</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1432</v>
+        <v>0.0204</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6738</v>
+        <v>0.0204</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4694</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3765</v>
+        <v>0.0204</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.1332</v>
+        <v>0.0204</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2432</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5406</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2262</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5202</v>
+        <v>-0.1188</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4846</v>
+        <v>-0.1188</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0355</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1258</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4892</v>
+        <v>-0.3833</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0984</v>
+        <v>-1.4872</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5875</v>
+        <v>1.1039</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0204</v>
+        <v>-3.1432</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0204</v>
+        <v>-1.6738</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1.4694</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0204</v>
+        <v>-2.3765</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0204</v>
+        <v>-1.1332</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-1.2432</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.7668</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.5406</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2262</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1188</v>
+        <v>0.2425</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1188</v>
+        <v>-0.2317</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.4742</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1258</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.644</v>
+        <v>-0.537</v>
       </c>
       <c r="E6" t="n">
         <v>0.0189</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3235</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.908</v>
+        <v>-0.801</v>
       </c>
       <c r="T6" t="n">
         <v>-0.6534</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2545</v>
+        <v>-0.1476</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7912</v>
+        <v>-0.7494</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1615</v>
+        <v>2.0162</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9527</v>
+        <v>-2.7656</v>
       </c>
       <c r="G7" t="n">
         <v>0.8552</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4981</v>
+        <v>-0.4562</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2247</v>
+        <v>0.0794</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7228</v>
+        <v>-0.5356</v>
       </c>
       <c r="V7" t="n">
         <v>-0.365</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4962</v>
+        <v>-2.2379</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2366</v>
+        <v>-1.7912</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2597</v>
+        <v>-0.4468</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1567</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6973</v>
+        <v>0.9556</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1445</v>
+        <v>0.5899</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5528</v>
+        <v>0.3657</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6659</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.091</v>
+        <v>-2.2794</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7015</v>
+        <v>-2.1304</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3896</v>
+        <v>-0.149</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1417</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3678</v>
+        <v>0.4439</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5411</v>
+        <v>0.03</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1733</v>
+        <v>0.4139</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5816</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3746</v>
+        <v>-6.0676</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.499</v>
+        <v>-7.192</v>
       </c>
       <c r="F10" t="n">
         <v>1.1244</v>
@@ -1234,10 +1234,10 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3741</v>
+        <v>0.6811</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6422</v>
+        <v>-0.3352</v>
       </c>
       <c r="U10" t="n">
         <v>1.0163</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.0527</v>
+        <v>-9.677099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.6193</v>
+        <v>-7.4576</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4333</v>
+        <v>-2.2195</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6131</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5285</v>
+        <v>-0.1529</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04</v>
+        <v>0.2017</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5685</v>
+        <v>-0.3546</v>
       </c>
       <c r="V11" t="n">
         <v>-0.365</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7945</v>
+        <v>-11.4975</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.903299999999998</v>
+        <v>-8.606400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8912</v>
+        <v>-2.8913</v>
       </c>
       <c r="G12" t="n">
         <v>-8.322900000000001</v>
@@ -1390,13 +1390,13 @@
         <v>9.792100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3968</v>
+        <v>1.6941</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7232999999999998</v>
+        <v>-0.4263999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1202</v>
+        <v>2.1205</v>
       </c>
       <c r="V12" t="n">
         <v>4.9239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3214</v>
+        <v>7.5841</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4216</v>
+        <v>5.1146</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8998</v>
+        <v>2.4695</v>
       </c>
       <c r="G13" t="n">
         <v>4.8348</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0007</v>
+        <v>0.262</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0576</v>
+        <v>-0.2494</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0583</v>
+        <v>0.5114</v>
       </c>
       <c r="V13" t="n">
         <v>0.3329</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2887</v>
+        <v>6.0349</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6019</v>
+        <v>3.4762</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6867</v>
+        <v>2.5587</v>
       </c>
       <c r="G14" t="n">
         <v>2.915</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8069</v>
+        <v>1.5531</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8379</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.969</v>
+        <v>0.8409</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3477</v>
+        <v>5.5773</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0171</v>
+        <v>1.9148</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3306</v>
+        <v>3.6625</v>
       </c>
       <c r="G15" t="n">
         <v>0.09760000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1544</v>
+        <v>0.3841</v>
       </c>
       <c r="T15" t="n">
-        <v>0.117</v>
+        <v>0.0147</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0374</v>
+        <v>0.3694</v>
       </c>
       <c r="V15" t="n">
         <v>2.1578</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8868</v>
+        <v>1.2816</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8032</v>
+        <v>0.9781</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.3034</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7154</v>
+        <v>1.0738</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0687</v>
+        <v>0.8058</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6466</v>
+        <v>0.2681</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6466</v>
+        <v>0.9823</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.7349</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6466</v>
+        <v>0.2473</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0687</v>
+        <v>0.0916</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0687</v>
+        <v>0.0708</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0832</v>
+        <v>0.2492</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1188</v>
+        <v>-0.0041</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0356</v>
+        <v>0.2533</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3329</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7773</v>
+        <v>1.0426</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7735</v>
+        <v>0.9055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0038</v>
+        <v>0.1371</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0738</v>
+        <v>0.7154</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8058</v>
+        <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2681</v>
+        <v>0.6466</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9823</v>
+        <v>0.6466</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7349</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2473</v>
+        <v>0.6466</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0916</v>
+        <v>0.0687</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0708</v>
+        <v>0.0687</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2551</v>
+        <v>0.0726</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2088</v>
+        <v>-0.0165</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0463</v>
+        <v>0.0891</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.696</v>
+        <v>0.8813</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.147</v>
+        <v>-0.0447</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8429</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>1.6273</v>
@@ -1858,13 +1858,13 @@
         <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3438</v>
+        <v>-0.1585</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.155</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2492</v>
+        <v>0.1486</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9377</v>
+        <v>0.3237</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6885</v>
+        <v>-0.175</v>
       </c>
       <c r="G19" t="n">
         <v>1.6897</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9132</v>
+        <v>0.8127</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2745</v>
+        <v>0.6605</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3613</v>
+        <v>0.1522</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1578</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. MENDÉZ POLLÁN</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0915</v>
+        <v>0.1207</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1958</v>
+        <v>-0.8984</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1044</v>
+        <v>1.0191</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0687</v>
+        <v>-1.046</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0687</v>
+        <v>-0.5866</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.4594</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.1825</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.3845</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2021</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0687</v>
+        <v>-0.8635</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0687</v>
+        <v>-0.2021</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.6615</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0356</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.8381</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0356</v>
+        <v>0.1995</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1014</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1143</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.733</v>
+        <v>-1.426</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6187</v>
+        <v>1.5174</v>
       </c>
       <c r="G21" t="n">
         <v>0.2856</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>0.054</v>
+        <v>0.2597</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.377</v>
       </c>
       <c r="U21" t="n">
-        <v>0.738</v>
+        <v>0.6367</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8249</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>Y. MENDÉZ POLLÁN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6712</v>
+        <v>-0.038</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3077</v>
+        <v>-0.1958</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6365</v>
+        <v>0.1578</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.046</v>
+        <v>0.0687</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5866</v>
+        <v>0.0687</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4594</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1825</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3845</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2021</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8635</v>
+        <v>0.0687</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2021</v>
+        <v>0.0687</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6615</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9585</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4305</v>
+        <v>0.0891</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2474</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1831</v>
+        <v>0.0891</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6176</v>
+        <v>-3.3491</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8993</v>
+        <v>-3.3876</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7184</v>
+        <v>0.0384</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0329</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8762</v>
+        <v>-0.6077</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.485</v>
+        <v>-0.9734</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3912</v>
+        <v>0.3657</v>
       </c>
       <c r="V23" t="n">
         <v>-1.492</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2777</v>
+        <v>-4.1696</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3809</v>
+        <v>-3.8692</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8968</v>
+        <v>-0.3003</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9062</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3715</v>
+        <v>-0.2633</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2474</v>
+        <v>-0.7358</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.124</v>
+        <v>0.4724</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>11.7948</v>
+        <v>15.2057</v>
       </c>
       <c r="E25" t="n">
-        <v>2.891299999999997</v>
+        <v>2.891199999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>8.9033</v>
+        <v>12.3145</v>
       </c>
       <c r="G25" t="n">
-        <v>8.322800000000003</v>
+        <v>8.322800000000001</v>
       </c>
       <c r="H25" t="n">
         <v>3.754800000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4.567899999999998</v>
+        <v>4.5679</v>
       </c>
       <c r="J25" t="n">
         <v>10.8337</v>
@@ -2389,7 +2389,7 @@
         <v>-2.5109</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6459000000000001</v>
+        <v>-0.6458999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-1.8649</v>
@@ -2404,22 +2404,22 @@
         <v>19.5849</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3969</v>
+        <v>2.0144</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.120200000000001</v>
+        <v>-2.1204</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7233999999999999</v>
+        <v>4.1347</v>
       </c>
       <c r="V25" t="n">
         <v>-4.923999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9702</v>
+        <v>3.970199999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.894299999999999</v>
+        <v>-8.894300000000001</v>
       </c>
     </row>
   </sheetData>
